--- a/AAII_Financials/Quarterly/NREF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NREF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="92">
   <si>
     <t>NREF</t>
   </si>
@@ -656,127 +656,128 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
@@ -795,86 +796,89 @@
       <c r="AI7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E8" s="3">
         <v>32600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>30000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>61300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>31700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>34300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>31400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3">
         <v>24300</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3">
         <v>14500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>23800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>33100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>32400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>36300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>23400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>35100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>35700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>20500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>27000</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
@@ -896,8 +900,11 @@
       <c r="AI8" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ8" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -908,13 +915,13 @@
         <v>300</v>
       </c>
       <c r="F9" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G9" s="3">
         <v>400</v>
       </c>
       <c r="H9" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I9" s="3">
         <v>300</v>
@@ -923,62 +930,62 @@
         <v>300</v>
       </c>
       <c r="K9" s="3">
+        <v>300</v>
+      </c>
+      <c r="L9" s="3">
         <v>400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>600</v>
-      </c>
-      <c r="M9" s="3">
-        <v>1000</v>
       </c>
       <c r="N9" s="3">
         <v>1000</v>
       </c>
       <c r="O9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P9" s="3">
         <v>1100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>11800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10000</v>
-      </c>
-      <c r="U9" s="3">
-        <v>9100</v>
       </c>
       <c r="V9" s="3">
         <v>9100</v>
       </c>
       <c r="W9" s="3">
+        <v>9100</v>
+      </c>
+      <c r="X9" s="3">
         <v>8900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4000</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
@@ -997,86 +1004,89 @@
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E10" s="3">
         <v>32300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>29700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>61000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>31300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>34000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>23900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>31000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>20700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-4200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>23300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-11800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-4400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>13600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>23100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>23300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>27200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>14500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>27300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>27800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>13200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>20600</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1098,8 +1108,11 @@
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1135,8 +1148,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1236,8 +1250,11 @@
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1337,37 +1354,40 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>100</v>
-      </c>
-      <c r="J14" s="3">
-        <v>200</v>
       </c>
       <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3">
+        <v>200</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
@@ -1381,8 +1401,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1390,8 +1410,8 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
@@ -1408,8 +1428,8 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1438,16 +1458,19 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E15" s="3">
         <v>1400</v>
-      </c>
-      <c r="E15" s="3">
-        <v>600</v>
       </c>
       <c r="F15" s="3">
         <v>600</v>
@@ -1456,7 +1479,7 @@
         <v>600</v>
       </c>
       <c r="H15" s="3">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="I15" s="3">
         <v>1100</v>
@@ -1468,13 +1491,13 @@
         <v>1100</v>
       </c>
       <c r="L15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M15" s="3">
         <v>2300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>500</v>
       </c>
       <c r="O15" s="3">
         <v>500</v>
@@ -1483,7 +1506,7 @@
         <v>500</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1539,8 +1562,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1573,8 +1599,9 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1582,80 +1609,80 @@
         <v>10000</v>
       </c>
       <c r="E17" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F17" s="3">
         <v>7800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4700</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1674,86 +1701,89 @@
       <c r="AI17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E18" s="3">
         <v>22600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>22200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>53000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>22400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>26000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>15300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>23500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-17100</v>
-      </c>
-      <c r="O18" s="3">
-        <v>9400</v>
       </c>
       <c r="P18" s="3">
         <v>9400</v>
       </c>
       <c r="Q18" s="3">
+        <v>9400</v>
+      </c>
+      <c r="R18" s="3">
         <v>-4300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>18100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>20900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>25200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>12200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>25100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>26200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>19300</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1775,8 +1805,11 @@
       <c r="AI18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1812,8 +1845,9 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1850,14 +1884,14 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1889,8 +1923,8 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
+      <c r="AB20" s="3">
+        <v>0</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
@@ -1913,65 +1947,68 @@
       <c r="AI20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E21" s="3">
         <v>24100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>22800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>53600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>23000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>27100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>16400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>24600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-12300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>19000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-16600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-8800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>19000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2014,8 +2051,11 @@
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2058,8 +2098,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2115,89 +2155,92 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E23" s="3">
         <v>22600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>24000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>50900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>22300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>26000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>15200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>23300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>17900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-17100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>18100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>21000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>25200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>12300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>25100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>26200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>11500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>19300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-22900</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2216,8 +2259,11 @@
       <c r="AI23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2260,8 +2306,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2317,8 +2363,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2418,89 +2467,92 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E26" s="3">
         <v>22600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>24000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>50900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>22300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>26000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>23300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>12100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>17900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-17100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>18100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>21000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>25200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>12300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>25100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>26200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>11500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>19300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-22900</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2519,89 +2571,92 @@
       <c r="AI26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E27" s="3">
         <v>10000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>11800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>35000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>13600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-15600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3900</v>
-      </c>
-      <c r="T27" s="3">
-        <v>12400</v>
       </c>
       <c r="U27" s="3">
         <v>12400</v>
       </c>
       <c r="V27" s="3">
+        <v>12400</v>
+      </c>
+      <c r="W27" s="3">
         <v>13200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>8400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>9300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2620,8 +2675,11 @@
       <c r="AI27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2721,8 +2779,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2822,8 +2883,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2923,8 +2987,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3024,8 +3091,11 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3062,14 +3132,14 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3101,8 +3171,8 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
+      <c r="AB32" s="3">
+        <v>0</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
@@ -3125,89 +3195,92 @@
       <c r="AI32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E33" s="3">
         <v>20300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>21400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>43100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>18800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>14600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3900</v>
-      </c>
-      <c r="T33" s="3">
-        <v>12400</v>
       </c>
       <c r="U33" s="3">
         <v>12400</v>
       </c>
       <c r="V33" s="3">
+        <v>12400</v>
+      </c>
+      <c r="W33" s="3">
         <v>13200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>8400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>9300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3226,8 +3299,11 @@
       <c r="AI33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3327,89 +3403,92 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E35" s="3">
         <v>20300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>21400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>43100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>18800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>14600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3900</v>
-      </c>
-      <c r="T35" s="3">
-        <v>12400</v>
       </c>
       <c r="U35" s="3">
         <v>12400</v>
       </c>
       <c r="V35" s="3">
+        <v>12400</v>
+      </c>
+      <c r="W35" s="3">
         <v>13200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>8400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>9300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3428,94 +3507,97 @@
       <c r="AI35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3534,8 +3616,11 @@
       <c r="AI38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3571,8 +3656,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3608,89 +3694,90 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E41" s="3">
         <v>22600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>31100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>34700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>38800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>20000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>52700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>35200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>26500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>22200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>30000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>14900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>30200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>18000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>200</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3709,8 +3796,11 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3810,71 +3900,74 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4681900</v>
+      </c>
+      <c r="E43" s="3">
         <v>4709000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4782600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4824700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4992300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5040500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5147000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5370400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6301000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6754900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6719400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6673700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7364400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7783900</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V43" s="3">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W43" s="3">
         <v>6400</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3890,8 +3983,8 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -3911,8 +4004,11 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3955,8 +4051,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4012,8 +4108,11 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4056,8 +4155,8 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4113,53 +4212,56 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4820100</v>
+      </c>
+      <c r="E46" s="3">
         <v>4734200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4817000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4846300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5006100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5063900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5154000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5409100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6308400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6774200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6736000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6686600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7385900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7824200</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4214,89 +4316,92 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>347400</v>
+      </c>
+      <c r="E47" s="3">
         <v>349300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>349900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>325200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>231400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>174100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>105200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>116700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>105000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>147000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>114600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>98700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>115200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>115000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7886400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8183900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7745500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7923000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8418000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8264300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8504000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5941300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6142100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6146900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3857200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2714000</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4315,8 +4420,11 @@
       <c r="AI47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4359,24 +4467,24 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3">
         <v>245200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>59900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>60400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>61300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>62300</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4392,8 +4500,8 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
@@ -4416,8 +4524,11 @@
       <c r="AI48" s="3">
         <v>0</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4517,8 +4628,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4618,8 +4732,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4719,80 +4836,83 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E52" s="3">
         <v>151100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>154300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>106600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>164900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>160700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>156800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>160100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>161600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>163800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>167800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>101000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>102100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>103400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3200</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4808,8 +4928,8 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF52" s="3">
-        <v>0</v>
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG52" s="3">
         <v>0</v>
@@ -4820,8 +4940,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4921,89 +5044,92 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5367600</v>
+      </c>
+      <c r="E54" s="3">
         <v>5234600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5321200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5278100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5402400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5398800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5416100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5685800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6574900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7085000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7018400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6886400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7603200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8042600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8154100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8275900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7861200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8021500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8513900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8296400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8536100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5960200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6176300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6165700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3859300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2715300</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5022,8 +5148,11 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5059,8 +5188,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5096,89 +5226,90 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E57" s="3">
         <v>14500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1600</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5197,88 +5328,91 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>270200</v>
+      </c>
+      <c r="E58" s="3">
         <v>462200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>554100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>546800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>606400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>432200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>409600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>386800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>417200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>341700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>303500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>298000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>333200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>350400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>331000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>351000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>312400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>297000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>286300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>222500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>177600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>162200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>161500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>160200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>60100</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="3" t="s">
-        <v>3</v>
+      <c r="AC58" s="3">
+        <v>0</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>3</v>
@@ -5292,14 +5426,17 @@
       <c r="AG58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH58" s="3">
-        <v>0</v>
+      <c r="AH58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5342,45 +5479,45 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
         <v>8000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>70800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>900</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5399,53 +5536,56 @@
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>299200</v>
+      </c>
+      <c r="E60" s="3">
         <v>493700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>581600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>574000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>630300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>454000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>429100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>406000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>434000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>364700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>318200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>311500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>348000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>366000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -5500,89 +5640,92 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4206000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3891700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3907700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3929100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4089600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4324300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4415300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4747000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5659400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6272100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6254700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6140700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6789100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7203600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7263900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7407500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7019600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7201600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7713000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7566200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7845600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5371500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5606800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5612900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3459400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2396300</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5601,8 +5744,11 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5645,8 +5791,8 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -5702,8 +5848,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5803,8 +5952,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5904,8 +6056,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6005,89 +6160,92 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4505200</v>
+      </c>
+      <c r="E66" s="3">
         <v>4385400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4489300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4503100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4719800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4778200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4844400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5153100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6093400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6636800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6572800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6452200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7137000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7569600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7770200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7924100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7495000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7662200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8275900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8066100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8391100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5825800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6048100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6041800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3773000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2632200</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6106,8 +6264,11 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6143,8 +6304,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6244,8 +6406,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6345,43 +6510,46 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>401000</v>
+      </c>
+      <c r="E70" s="3">
         <v>378000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>361700</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>305600</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>245600</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>189000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>149100</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>110700</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>69200</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>27500</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
-        <v>-8600</v>
+        <v>0</v>
       </c>
       <c r="O70" s="3">
         <v>-8600</v>
@@ -6420,7 +6588,7 @@
         <v>-8600</v>
       </c>
       <c r="AA70" s="3">
-        <v>0</v>
+        <v>-8600</v>
       </c>
       <c r="AB70" s="3">
         <v>0</v>
@@ -6446,8 +6614,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6547,89 +6718,92 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-16300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-16500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-19000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-44700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-47500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-54900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-54100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-61100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-59300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-35800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-37200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-9300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>31000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>33800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>28400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>20600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>9200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6648,8 +6822,11 @@
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6749,8 +6926,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6850,8 +7030,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6951,89 +7134,92 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>379600</v>
+      </c>
+      <c r="E76" s="3">
         <v>388600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>387900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>372000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>344800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>340300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>333100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>332500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>324200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>333800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>355900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>353500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>380100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>385700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>392500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>360400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>374800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>367800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>246600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>238900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>153600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>142900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>136800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>132400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>86300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>83100</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7052,8 +7238,11 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7153,94 +7342,97 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
@@ -7259,89 +7451,92 @@
       <c r="AI80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E81" s="3">
         <v>20300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>21400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>43100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>18800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>14600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3900</v>
-      </c>
-      <c r="T81" s="3">
-        <v>12400</v>
       </c>
       <c r="U81" s="3">
         <v>12400</v>
       </c>
       <c r="V81" s="3">
+        <v>12400</v>
+      </c>
+      <c r="W81" s="3">
         <v>13200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>8400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>9300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
@@ -7360,8 +7555,11 @@
       <c r="AI81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7397,13 +7595,14 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="E83" s="3">
         <v>1100</v>
@@ -7415,13 +7614,13 @@
         <v>1100</v>
       </c>
       <c r="H83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I83" s="3">
         <v>2300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>500</v>
       </c>
       <c r="K83" s="3">
         <v>500</v>
@@ -7436,25 +7635,25 @@
         <v>500</v>
       </c>
       <c r="O83" s="3">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="P83" s="3">
         <v>900</v>
       </c>
       <c r="Q83" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="R83" s="3">
         <v>500</v>
       </c>
       <c r="S83" s="3">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="T83" s="3">
         <v>900</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>900</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
@@ -7471,8 +7670,8 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -7498,8 +7697,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7599,8 +7801,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7700,8 +7905,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7801,8 +8009,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7902,8 +8113,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8003,89 +8217,92 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E89" s="3">
         <v>9400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>16000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>15000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>11200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>12900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>38500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>12100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>14400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>13800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>11900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>6800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>5100</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
@@ -8104,8 +8321,11 @@
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8141,8 +8361,9 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8185,8 +8406,8 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -8195,11 +8416,11 @@
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-184600</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
@@ -8242,8 +8463,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8343,8 +8567,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8444,89 +8671,92 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E94" s="3">
         <v>84700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>41900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>190100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>18300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>71300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>220600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>138900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>51600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>545400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>101900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>208100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>364600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>66700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>99700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>141600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>498200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>211100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>321300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>151500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-26300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>71400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>41900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-88700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-52300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>30900</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
@@ -8545,8 +8775,11 @@
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8582,43 +8815,44 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E96" s="3">
         <v>12300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>9400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>8400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>8900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>8800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>9700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>7800</v>
-      </c>
-      <c r="K96" s="3">
-        <v>8700</v>
       </c>
       <c r="L96" s="3">
         <v>8700</v>
       </c>
       <c r="M96" s="3">
+        <v>8700</v>
+      </c>
+      <c r="N96" s="3">
         <v>12600</v>
-      </c>
-      <c r="N96" s="3">
-        <v>11800</v>
       </c>
       <c r="O96" s="3">
         <v>11800</v>
@@ -8627,7 +8861,7 @@
         <v>11800</v>
       </c>
       <c r="Q96" s="3">
-        <v>-7500</v>
+        <v>11800</v>
       </c>
       <c r="R96" s="3">
         <v>-7500</v>
@@ -8636,35 +8870,35 @@
         <v>-7500</v>
       </c>
       <c r="T96" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="U96" s="3">
         <v>-7200</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-4400</v>
       </c>
       <c r="V96" s="3">
         <v>-4400</v>
       </c>
       <c r="W96" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="X96" s="3">
         <v>-3100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-2100</v>
       </c>
       <c r="AA96" s="3">
         <v>-2100</v>
       </c>
       <c r="AB96" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -8683,8 +8917,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8784,8 +9021,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8885,8 +9125,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8986,89 +9229,92 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>94900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-103200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-24600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-190300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-31400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-70900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-256600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-122300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-56100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-560500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-101300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-222700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-390900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-61700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-255200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-179600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-492300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-102100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-324800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-172000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>27800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-98500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-38200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>96600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>18100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
@@ -9087,8 +9333,11 @@
       <c r="AI100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9131,8 +9380,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -9188,89 +9437,92 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>16400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-31700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>31400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-18700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>20000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-29900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>18800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>8700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>15200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>15500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>17000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>200</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
@@ -9287,6 +9539,9 @@
         <v>3</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
